--- a/cicada_generator/lib/WHO/antigen/Diphtheria.xlsx
+++ b/cicada_generator/lib/WHO/antigen/Diphtheria.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="6-dose series" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Antigen Series Overview" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Change History" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="FAQ" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Vaccine Recommendation Category" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Immunity" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Contraindications" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="6-dose series" sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +17,142 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="153">
+  <si>
+    <t xml:space="preserve">Overview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This workbook holds the immunization supporting data for Diphtheria: the series a patient may be on, the doses in each series, and the evidence of immunity and contraindications that apply. It follows the layout of the CDC CDSi Antigen Supporting Data workbooks (version 4.65), so that one parser reads every workbook.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publication Date: n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change #</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason for Change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDSi Manifestation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">If the Best Patient Series for the patient is…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AND the patient's current age is on or after the Begin Age and before the End Age…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AND the Target Dose being forecasted is…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AND the patient's risk factor is one of the Included Indications (and not one of the Excluded Indications)…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THEN the Vaccine Recommendation Category is…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccine Recommendation Category Specific Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excel Worksheet Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best Patient Series Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient Begin Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient End Age (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Target Dose Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Included Indication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excluded Indication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccine Recommendation Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical History Immunity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunity Guideline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Birth Date Immunity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunity Birth Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunity Country of Birth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunity Exclusion Condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antigen Contraindication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contraindication (Code)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administrative Guidance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contraindication Begin Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contraindication End Age (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccine Contraindication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccine Type (CVX)</t>
+  </si>
   <si>
     <t xml:space="preserve">Series Name</t>
   </si>
@@ -32,21 +172,57 @@
     <t xml:space="preserve">DTP</t>
   </si>
   <si>
+    <t xml:space="preserve">Text</t>
+  </si>
+  <si>
     <t xml:space="preserve">Series Type</t>
   </si>
   <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
     <t xml:space="preserve">Standard</t>
   </si>
   <si>
     <t xml:space="preserve">Equivalent Series Groups</t>
   </si>
   <si>
-    <t xml:space="preserve">n/a</t>
+    <t xml:space="preserve">Series Groups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required Gender</t>
   </si>
   <si>
     <t xml:space="preserve">Select Patient Series</t>
   </si>
   <si>
+    <t xml:space="preserve">Default Series</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series Group Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series Priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series Preference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum Age To Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum Age To Start</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
@@ -59,6 +235,18 @@
     <t xml:space="preserve">A</t>
   </si>
   <si>
+    <t xml:space="preserve">Indication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observation (Code)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indication Begin Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indication End Age (less than)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Series Dose</t>
   </si>
   <si>
@@ -68,12 +256,81 @@
     <t xml:space="preserve">Age</t>
   </si>
   <si>
+    <t xml:space="preserve">Absolute Minimum Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earliest Recommended Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest Recommended Age (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum Age (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cessation Date</t>
+  </si>
+  <si>
     <t xml:space="preserve">6 weeks</t>
   </si>
   <si>
+    <t xml:space="preserve">Preferable Interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Immediate Previous Dose Administered? Y/N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Target Dose # in Series</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Most Recent (CVX List)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Relevant Observation (Code)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute Minimum Interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum Interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earliest Recommended Interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest Recommended Interval (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interval Priority Flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowable Interval</t>
+  </si>
+  <si>
     <t xml:space="preserve">Preferable Vaccine</t>
   </si>
   <si>
+    <t xml:space="preserve">Vaccine Type Begin Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccine Type End Age (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trade Name (MVX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volume (in ml)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Vaccine Type (Y/N)</t>
+  </si>
+  <si>
     <t xml:space="preserve">DTP-HepB-Hib (Pentavalent) (198)</t>
   </si>
   <si>
@@ -101,16 +358,70 @@
     <t xml:space="preserve">DTaP-IPV (130)</t>
   </si>
   <si>
+    <t xml:space="preserve">Inadvertent Vaccine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conditional Skip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skip Context</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set Logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition Logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Begin Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End Age (less than)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dose Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dose Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dose Count Logic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccine Types (CVX List)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Recurring Dose</t>
   </si>
   <si>
+    <t xml:space="preserve">Recurring Dose (Yes/No)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seasonal Recommendation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dose 2</t>
   </si>
   <si>
     <t xml:space="preserve">10 weeks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preferable Interval</t>
   </si>
   <si>
     <t xml:space="preserve">4 weeks</t>
@@ -405,13 +716,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15.75" defaultColWidth="14.43"/>
-  <sheetData/>
-  <drawing r:id="rId1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -421,15 +738,148 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -437,55 +887,182 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -493,180 +1070,171 @@
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>62</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>54</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>9</v>
+        <v>74</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>12</v>
+        <v>79</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="18">
@@ -674,172 +1242,247 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>30</v>
+        <v>86</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>9</v>
+        <v>94</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>9</v>
+        <v>100</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>29</v>
+        <v>109</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>12</v>
+        <v>44</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -847,172 +1490,217 @@
         <v>15</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>34</v>
+        <v>106</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>9</v>
+        <v>117</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38">
@@ -1020,167 +1708,185 @@
         <v>15</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>21</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>23</v>
+        <v>84</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>22</v>
+        <v>134</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>9</v>
+        <v>134</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>9</v>
+        <v>90</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>12</v>
+        <v>88</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="47">
@@ -1188,218 +1894,227 @@
         <v>15</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>40</v>
+        <v>3</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>9</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>12</v>
+        <v>115</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="R58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S58" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="T58" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="59">
@@ -1407,190 +2122,2094 @@
         <v>15</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>47</v>
+        <v>3</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>9</v>
+        <v>81</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>45</v>
+        <v>137</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>9</v>
+        <v>137</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>9</v>
+        <v>90</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>12</v>
+        <v>105</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P81" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q81" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="R81" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S81" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="T81" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T82" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P103" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q103" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="R103" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S103" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="T103" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T104" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L113" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M128" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N128" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O128" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P128" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q128" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="R128" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S128" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="T128" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T129" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L137" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L138" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L151" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M151" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N151" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="O151" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P151" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q151" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="R151" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="S151" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="T151" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T152" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
